--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="271" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90B62574-A6C6-4710-A454-9838C905E218}"/>
+  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36176287-9326-43D2-A6E1-B28BE3FEB7AE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -2109,25 +2112,47 @@
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B31" s="14">
+        <v>520</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>50</v>
+      </c>
+      <c r="F31" s="14">
+        <v>50</v>
+      </c>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36176287-9326-43D2-A6E1-B28BE3FEB7AE}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91FB71FF-FC70-449F-8FB2-6B5A91D99ED5}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2156,25 +2156,47 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="14">
+        <v>450</v>
+      </c>
+      <c r="C32" s="14">
+        <v>30</v>
+      </c>
+      <c r="D32" s="14">
+        <v>90</v>
+      </c>
+      <c r="E32" s="14">
+        <v>50</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>100</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>420</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91FB71FF-FC70-449F-8FB2-6B5A91D99ED5}"/>
+  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DC4B312-2DD3-41B9-87B7-A301F6101730}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2200,25 +2200,47 @@
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="14">
+        <v>520</v>
+      </c>
+      <c r="C33" s="14">
+        <v>30</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>50</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>6</v>
+      </c>
+      <c r="H33" s="14">
+        <v>50</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="305" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DC4B312-2DD3-41B9-87B7-A301F6101730}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{323E1363-A66E-40F6-85E3-657B13D3F912}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2244,25 +2244,47 @@
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="14">
+        <v>520</v>
+      </c>
+      <c r="C34" s="14">
+        <v>30</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>50</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>6</v>
+      </c>
+      <c r="H34" s="14">
+        <v>50</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{323E1363-A66E-40F6-85E3-657B13D3F912}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD2CE79-9183-40A8-8926-AB0E14698EB8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2288,91 +2288,179 @@
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="14">
+        <v>520</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>120</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>200</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>350</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>520</v>
+      </c>
+      <c r="C36" s="14">
+        <v>30</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>50</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>50</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14">
+        <v>600</v>
+      </c>
+      <c r="C37" s="14">
+        <v>50</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>200</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14">
+        <v>700</v>
+      </c>
+      <c r="C38" s="14">
+        <v>50</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>200</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD2CE79-9183-40A8-8926-AB0E14698EB8}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA674850-3A1D-4093-9785-B1F6EE006D23}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2464,25 +2464,47 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B39" s="14">
+        <v>520</v>
+      </c>
+      <c r="C39" s="14">
+        <v>50</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>6</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA674850-3A1D-4093-9785-B1F6EE006D23}"/>
+  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{909A2892-0704-4D2B-8C70-D36D93856E47}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2508,25 +2508,47 @@
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B40" s="14">
+        <v>520</v>
+      </c>
+      <c r="C40" s="14">
+        <v>50</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>120</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>60</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>270</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{909A2892-0704-4D2B-8C70-D36D93856E47}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9DBF0E0-D190-4CC1-9895-18DA7F308CF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2552,25 +2552,47 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B41" s="14">
+        <v>520</v>
+      </c>
+      <c r="C41" s="14">
+        <v>50</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>50</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9DBF0E0-D190-4CC1-9895-18DA7F308CF1}"/>
+  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB1CA908-3DB0-4315-9371-CCB542FA1632}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Prajoti Nayak</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>MCA/D1P2636</t>
   </si>
   <si>
@@ -227,6 +224,9 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>september</t>
   </si>
 </sst>
 </file>
@@ -935,7 +935,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -943,7 +943,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1049,7 +1049,7 @@
         <v>50</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N6" s="12" t="s">
         <v>51</v>
@@ -1089,13 +1089,13 @@
         <v>0</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M7" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N7" s="17"/>
     </row>
@@ -1139,7 +1139,7 @@
         <v>50</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N8" s="17"/>
     </row>
@@ -1183,7 +1183,7 @@
         <v>50</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N9" s="17"/>
     </row>
@@ -1224,10 +1224,10 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N10" s="17"/>
     </row>
@@ -1268,10 +1268,10 @@
         <v>49</v>
       </c>
       <c r="L11" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N11" s="17"/>
     </row>
@@ -1312,10 +1312,10 @@
         <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N12" s="17"/>
     </row>
@@ -1359,7 +1359,7 @@
         <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N13" s="17"/>
     </row>
@@ -1403,7 +1403,7 @@
         <v>50</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N14" s="17"/>
     </row>
@@ -1447,7 +1447,7 @@
         <v>50</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N15" s="17"/>
     </row>
@@ -1491,7 +1491,7 @@
         <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" s="17"/>
     </row>
@@ -1529,13 +1529,13 @@
         <v>620</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17" s="17"/>
     </row>
@@ -1573,13 +1573,13 @@
         <v>620</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N18" s="17"/>
     </row>
@@ -1617,13 +1617,13 @@
         <v>350</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N19" s="17"/>
     </row>
@@ -1667,7 +1667,7 @@
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N20" s="17"/>
     </row>
@@ -1711,7 +1711,7 @@
         <v>50</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N21" s="17"/>
     </row>
@@ -1755,7 +1755,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N22" s="17"/>
     </row>
@@ -1799,7 +1799,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N23" s="17"/>
     </row>
@@ -1840,10 +1840,10 @@
         <v>49</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N24" s="17"/>
     </row>
@@ -1887,7 +1887,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N25" s="17"/>
     </row>
@@ -1928,10 +1928,10 @@
         <v>49</v>
       </c>
       <c r="L26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N26" s="17"/>
     </row>
@@ -1975,7 +1975,7 @@
         <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N27" s="17"/>
     </row>
@@ -2016,10 +2016,10 @@
         <v>49</v>
       </c>
       <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N28" s="17"/>
     </row>
@@ -2063,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N29" s="17"/>
     </row>
@@ -2107,7 +2107,7 @@
         <v>50</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N30" s="17"/>
     </row>
@@ -2145,13 +2145,13 @@
         <v>640</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="L31" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="M31" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N31" s="17"/>
     </row>
@@ -2195,7 +2195,7 @@
         <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N32" s="17"/>
     </row>
@@ -2233,13 +2233,13 @@
         <v>370</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N33" s="17"/>
     </row>
@@ -2280,10 +2280,10 @@
         <v>49</v>
       </c>
       <c r="L34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="16" t="s">
         <v>57</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N34" s="17"/>
     </row>
@@ -2327,7 +2327,7 @@
         <v>50</v>
       </c>
       <c r="M35" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N35" s="17"/>
     </row>
@@ -2371,7 +2371,7 @@
         <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N36" s="17"/>
     </row>
@@ -2409,13 +2409,13 @@
         <v>470</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N37" s="17"/>
     </row>
@@ -2453,13 +2453,13 @@
         <v>370</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N38" s="17"/>
     </row>
@@ -2500,10 +2500,10 @@
         <v>49</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N39" s="17"/>
     </row>
@@ -2547,7 +2547,7 @@
         <v>50</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N40" s="17"/>
     </row>
@@ -2585,102 +2585,190 @@
         <v>280</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L41" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="17"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="14">
+        <v>520</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>120</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>150</v>
+      </c>
+      <c r="G42" s="14">
+        <v>3</v>
+      </c>
+      <c r="H42" s="14">
+        <v>60</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N42" s="17"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B43" s="14">
+        <v>600</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="1"/>
+        <v>360</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N43" s="17"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B44" s="14">
+        <v>600</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>200</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N44" s="17"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="14">
+        <v>600</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>120</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>300</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M45" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627879.xlsx
+++ b/12627879.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7068eb44e1960581/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="440" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB1CA908-3DB0-4315-9371-CCB542FA1632}"/>
+  <xr:revisionPtr revIDLastSave="501" documentId="13_ncr:1_{781AF014-0C27-4563-8817-02ADB3B2A4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85611760-EB9B-4C65-8271-C963725F5752}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2772,113 +2772,222 @@
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="14">
+        <v>520</v>
+      </c>
+      <c r="C46" s="14">
+        <v>60</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>60</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B47" s="14">
+        <v>520</v>
+      </c>
+      <c r="C47" s="14">
+        <v>60</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>60</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>5</v>
+      </c>
+      <c r="H47" s="14">
+        <v>120</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B48" s="14">
+        <v>520</v>
+      </c>
+      <c r="C48" s="14">
+        <v>30</v>
+      </c>
+      <c r="D48" s="14">
+        <v>60</v>
+      </c>
+      <c r="E48" s="14">
+        <v>60</v>
+      </c>
+      <c r="F48" s="14">
+        <v>300</v>
+      </c>
+      <c r="G48" s="14">
+        <v>5</v>
+      </c>
+      <c r="H48" s="14">
+        <v>120</v>
+      </c>
+      <c r="I48" s="15">
+        <v>1090</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N48" s="17"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B49" s="14">
+        <v>520</v>
+      </c>
+      <c r="C49" s="14">
+        <v>60</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>120</v>
+      </c>
+      <c r="F49" s="14">
+        <v>100</v>
+      </c>
+      <c r="G49" s="14">
+        <v>1</v>
+      </c>
+      <c r="H49" s="14">
+        <v>200</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+        <v>320</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N49" s="17"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B50" s="14">
+        <v>520</v>
+      </c>
+      <c r="C50" s="14">
+        <v>120</v>
+      </c>
+      <c r="D50" s="14">
+        <v>120</v>
+      </c>
+      <c r="E50" s="14">
+        <v>60</v>
+      </c>
+      <c r="F50" s="14">
+        <v>300</v>
+      </c>
+      <c r="G50" s="14">
+        <v>6</v>
+      </c>
+      <c r="H50" s="14">
+        <v>300</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>20</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
